--- a/data/stocks_20260330_232910.xlsx
+++ b/data/stocks_20260330_232910.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:T39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,10 +519,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>000858</t>
-        </is>
+      <c r="A2" t="n">
+        <v>858</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -585,10 +583,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>300750</t>
-        </is>
+      <c r="A3" t="n">
+        <v>300750</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -651,10 +647,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>600030</t>
-        </is>
+      <c r="A4" t="n">
+        <v>600030</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -717,10 +711,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>600118</t>
-        </is>
+      <c r="A5" t="n">
+        <v>600118</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -783,10 +775,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>300308</t>
-        </is>
+      <c r="A6" t="n">
+        <v>300308</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -849,10 +839,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>601398</t>
-        </is>
+      <c r="A7" t="n">
+        <v>601398</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -915,10 +903,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>601919</t>
-        </is>
+      <c r="A8" t="n">
+        <v>601919</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -981,10 +967,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>002261</t>
-        </is>
+      <c r="A9" t="n">
+        <v>2261</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1047,10 +1031,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>688041</t>
-        </is>
+      <c r="A10" t="n">
+        <v>688041</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1113,10 +1095,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>300502</t>
-        </is>
+      <c r="A11" t="n">
+        <v>300502</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1179,10 +1159,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>300394</t>
-        </is>
+      <c r="A12" t="n">
+        <v>300394</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1245,10 +1223,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>000988</t>
-        </is>
+      <c r="A13" t="n">
+        <v>988</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1311,10 +1287,8 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>603986</t>
-        </is>
+      <c r="A14" t="n">
+        <v>603986</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1377,10 +1351,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>688525</t>
-        </is>
+      <c r="A15" t="n">
+        <v>688525</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1443,10 +1415,8 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>300042</t>
-        </is>
+      <c r="A16" t="n">
+        <v>300042</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1509,10 +1479,8 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>300302</t>
-        </is>
+      <c r="A17" t="n">
+        <v>300302</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1575,10 +1543,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>000020</t>
-        </is>
+      <c r="A18" t="n">
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1641,10 +1607,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>603881</t>
-        </is>
+      <c r="A19" t="n">
+        <v>603881</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1707,10 +1671,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>300017</t>
-        </is>
+      <c r="A20" t="n">
+        <v>300017</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1773,10 +1735,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>300418</t>
-        </is>
+      <c r="A21" t="n">
+        <v>300418</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1839,10 +1799,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>002230</t>
-        </is>
+      <c r="A22" t="n">
+        <v>2230</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1905,10 +1863,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>300058</t>
-        </is>
+      <c r="A23" t="n">
+        <v>300058</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1971,10 +1927,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>300496</t>
-        </is>
+      <c r="A24" t="n">
+        <v>300496</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2037,10 +1991,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>000547</t>
-        </is>
+      <c r="A25" t="n">
+        <v>547</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2103,10 +2055,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>002202</t>
-        </is>
+      <c r="A26" t="n">
+        <v>2202</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2169,10 +2119,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>301128</t>
-        </is>
+      <c r="A27" t="n">
+        <v>301128</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2229,6 +2177,774 @@
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>601899</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>紫金矿业</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="F28" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.908</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.864</v>
+      </c>
+      <c r="J28" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="K28" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="L28" t="n">
+        <v>62.96</v>
+      </c>
+      <c r="M28" t="n">
+        <v>23690.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>31535.3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P28" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>600219</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>南山铝业</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F29" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.356</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.308</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.34</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="L29" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="M29" t="n">
+        <v>56862.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>31175.02</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="P29" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>601939</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>建设银行</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="J30" t="n">
+        <v>84.95999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="L30" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11863.78</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10818.86</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="R30" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>600048</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>保利发展</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="E31" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.242</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0.207</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7514.07</v>
+      </c>
+      <c r="N31" t="n">
+        <v>12276.88</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>600941</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>中国移动</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E32" t="n">
+        <v>93.68000000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>95.63</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.461</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.067</v>
+      </c>
+      <c r="J32" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="M32" t="n">
+        <v>948.13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1113.81</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="R32" t="n">
+        <v>92.29000000000001</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2352</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>顺丰控股</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>36.76</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="E33" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="F33" t="n">
+        <v>36.59</v>
+      </c>
+      <c r="G33" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.315</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="J33" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="K33" t="n">
+        <v>44.17</v>
+      </c>
+      <c r="L33" t="n">
+        <v>72.87</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1263.27</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2235.34</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P33" t="n">
+        <v>36.72</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="R33" t="n">
+        <v>36.65</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>603803</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>瑞斯康达</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="E34" t="n">
+        <v>14.55</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="K34" t="n">
+        <v>67.98</v>
+      </c>
+      <c r="L34" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="M34" t="n">
+        <v>5791.29</v>
+      </c>
+      <c r="N34" t="n">
+        <v>7252.99</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="R34" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2624</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>完美世界</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="E35" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.597</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.432</v>
+      </c>
+      <c r="J35" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="K35" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="L35" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4083.75</v>
+      </c>
+      <c r="N35" t="n">
+        <v>5107.03</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P35" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="R35" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2558</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>巨人网络</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="E36" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="F36" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-2.091</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2.073</v>
+      </c>
+      <c r="J36" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="K36" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="L36" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2764.53</v>
+      </c>
+      <c r="N36" t="n">
+        <v>4055.24</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P36" t="n">
+        <v>31.58</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="R36" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>601088</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>中国神华</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="E37" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="F37" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="G37" t="n">
+        <v>47.74</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="J37" t="n">
+        <v>35.84</v>
+      </c>
+      <c r="K37" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="L37" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2812.65</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4898.09</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P37" t="n">
+        <v>47.89</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="R37" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>600963</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>岳阳林纸</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.286</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-0.213</v>
+      </c>
+      <c r="J38" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="L38" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3637.94</v>
+      </c>
+      <c r="N38" t="n">
+        <v>5112.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="R38" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>601877</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>正泰电器</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>33.22</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="E39" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="F39" t="n">
+        <v>34.62</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="J39" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="K39" t="n">
+        <v>24.77</v>
+      </c>
+      <c r="L39" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3407.57</v>
+      </c>
+      <c r="N39" t="n">
+        <v>5863.85</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P39" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="R39" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>

--- a/data/stocks_20260330_232910.xlsx
+++ b/data/stocks_20260330_232910.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T39"/>
+  <dimension ref="A1:T37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,60 +1032,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>215.73</v>
+        <v>458.38</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.36</v>
+        <v>2.45</v>
       </c>
       <c r="E10" t="n">
-        <v>217.21</v>
+        <v>461.4</v>
       </c>
       <c r="F10" t="n">
-        <v>219.06</v>
+        <v>450.51</v>
       </c>
       <c r="G10" t="n">
-        <v>229.71</v>
+        <v>421.03</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.291</v>
+        <v>19.77</v>
       </c>
       <c r="I10" t="n">
-        <v>-8.538</v>
+        <v>15.552</v>
       </c>
       <c r="J10" t="n">
-        <v>39.63</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>31.18</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>56.54</v>
+        <v>59.85</v>
       </c>
       <c r="M10" t="n">
-        <v>1461.24</v>
+        <v>2552.54</v>
       </c>
       <c r="N10" t="n">
-        <v>1946.81</v>
+        <v>4456.72</v>
       </c>
       <c r="O10" t="n">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="P10" t="n">
-        <v>218.6</v>
+        <v>445.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>218.88</v>
+        <v>464</v>
       </c>
       <c r="R10" t="n">
-        <v>213.07</v>
+        <v>445.2</v>
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
@@ -1096,60 +1096,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>458.38</v>
+        <v>316.81</v>
       </c>
       <c r="D11" t="n">
-        <v>2.45</v>
+        <v>-0.25</v>
       </c>
       <c r="E11" t="n">
-        <v>461.4</v>
+        <v>315.24</v>
       </c>
       <c r="F11" t="n">
-        <v>450.51</v>
+        <v>307.8</v>
       </c>
       <c r="G11" t="n">
-        <v>421.03</v>
+        <v>317.72</v>
       </c>
       <c r="H11" t="n">
-        <v>19.77</v>
+        <v>4.867</v>
       </c>
       <c r="I11" t="n">
-        <v>15.552</v>
+        <v>7.129</v>
       </c>
       <c r="J11" t="n">
-        <v>68.40000000000001</v>
+        <v>58.28</v>
       </c>
       <c r="K11" t="n">
-        <v>72.68000000000001</v>
+        <v>53.52</v>
       </c>
       <c r="L11" t="n">
-        <v>59.85</v>
+        <v>67.78</v>
       </c>
       <c r="M11" t="n">
-        <v>2552.54</v>
+        <v>2310.79</v>
       </c>
       <c r="N11" t="n">
-        <v>4456.72</v>
+        <v>3477.81</v>
       </c>
       <c r="O11" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="P11" t="n">
-        <v>445.2</v>
+        <v>314.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>464</v>
+        <v>322</v>
       </c>
       <c r="R11" t="n">
-        <v>445.2</v>
+        <v>308</v>
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
@@ -1160,60 +1160,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>316.81</v>
+        <v>106.95</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.25</v>
+        <v>-2.33</v>
       </c>
       <c r="E12" t="n">
-        <v>315.24</v>
+        <v>109.91</v>
       </c>
       <c r="F12" t="n">
-        <v>307.8</v>
+        <v>112.48</v>
       </c>
       <c r="G12" t="n">
-        <v>317.72</v>
+        <v>114.22</v>
       </c>
       <c r="H12" t="n">
-        <v>4.867</v>
+        <v>4.947</v>
       </c>
       <c r="I12" t="n">
-        <v>7.129</v>
+        <v>7.523</v>
       </c>
       <c r="J12" t="n">
-        <v>58.28</v>
+        <v>21.51</v>
       </c>
       <c r="K12" t="n">
-        <v>53.52</v>
+        <v>25.58</v>
       </c>
       <c r="L12" t="n">
-        <v>67.78</v>
+        <v>13.37</v>
       </c>
       <c r="M12" t="n">
-        <v>2310.79</v>
+        <v>5936.04</v>
       </c>
       <c r="N12" t="n">
-        <v>3477.81</v>
+        <v>12477.64</v>
       </c>
       <c r="O12" t="n">
-        <v>0.66</v>
+        <v>0.48</v>
       </c>
       <c r="P12" t="n">
-        <v>314.16</v>
+        <v>109</v>
       </c>
       <c r="Q12" t="n">
-        <v>322</v>
+        <v>110.5</v>
       </c>
       <c r="R12" t="n">
-        <v>308</v>
+        <v>105.57</v>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
@@ -1224,60 +1224,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>106.95</v>
+        <v>255.85</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.33</v>
+        <v>-1.09</v>
       </c>
       <c r="E13" t="n">
-        <v>109.91</v>
+        <v>265.72</v>
       </c>
       <c r="F13" t="n">
-        <v>112.48</v>
+        <v>280.31</v>
       </c>
       <c r="G13" t="n">
-        <v>114.22</v>
+        <v>281.26</v>
       </c>
       <c r="H13" t="n">
-        <v>4.947</v>
+        <v>-8.128</v>
       </c>
       <c r="I13" t="n">
-        <v>7.523</v>
+        <v>-4.745</v>
       </c>
       <c r="J13" t="n">
-        <v>21.51</v>
+        <v>25.63</v>
       </c>
       <c r="K13" t="n">
-        <v>25.58</v>
+        <v>33.05</v>
       </c>
       <c r="L13" t="n">
-        <v>13.37</v>
+        <v>10.78</v>
       </c>
       <c r="M13" t="n">
-        <v>5936.04</v>
+        <v>2146.96</v>
       </c>
       <c r="N13" t="n">
-        <v>12477.64</v>
+        <v>2956.06</v>
       </c>
       <c r="O13" t="n">
-        <v>0.48</v>
+        <v>0.73</v>
       </c>
       <c r="P13" t="n">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="Q13" t="n">
-        <v>110.5</v>
+        <v>259.54</v>
       </c>
       <c r="R13" t="n">
-        <v>105.57</v>
+        <v>250.03</v>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
@@ -1288,60 +1288,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>255.85</v>
+        <v>44.26</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.09</v>
+        <v>-0.41</v>
       </c>
       <c r="E14" t="n">
-        <v>265.72</v>
+        <v>45.92</v>
       </c>
       <c r="F14" t="n">
-        <v>280.31</v>
+        <v>49.8</v>
       </c>
       <c r="G14" t="n">
-        <v>281.26</v>
+        <v>43.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.128</v>
+        <v>2.804</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.745</v>
+        <v>3.357</v>
       </c>
       <c r="J14" t="n">
-        <v>25.63</v>
+        <v>24.59</v>
       </c>
       <c r="K14" t="n">
-        <v>33.05</v>
+        <v>41.96</v>
       </c>
       <c r="L14" t="n">
-        <v>10.78</v>
+        <v>-10.14</v>
       </c>
       <c r="M14" t="n">
-        <v>2146.96</v>
+        <v>1921.34</v>
       </c>
       <c r="N14" t="n">
-        <v>2956.06</v>
+        <v>3175.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="P14" t="n">
-        <v>252</v>
+        <v>44.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>259.54</v>
+        <v>45.32</v>
       </c>
       <c r="R14" t="n">
-        <v>250.03</v>
+        <v>43.65</v>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
@@ -1352,60 +1352,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>231.99</v>
+        <v>20.85</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.69</v>
+        <v>-1.33</v>
       </c>
       <c r="E15" t="n">
-        <v>238.84</v>
+        <v>21.64</v>
       </c>
       <c r="F15" t="n">
-        <v>239.51</v>
+        <v>22.73</v>
       </c>
       <c r="G15" t="n">
-        <v>220.67</v>
+        <v>21</v>
       </c>
       <c r="H15" t="n">
-        <v>15.012</v>
+        <v>0.531</v>
       </c>
       <c r="I15" t="n">
-        <v>15.043</v>
+        <v>0.622</v>
       </c>
       <c r="J15" t="n">
-        <v>53.43</v>
+        <v>21.22</v>
       </c>
       <c r="K15" t="n">
-        <v>61.97</v>
+        <v>37.06</v>
       </c>
       <c r="L15" t="n">
-        <v>36.34</v>
+        <v>-10.44</v>
       </c>
       <c r="M15" t="n">
-        <v>3094.59</v>
+        <v>2033.72</v>
       </c>
       <c r="N15" t="n">
-        <v>4359.55</v>
+        <v>4048.8</v>
       </c>
       <c r="O15" t="n">
-        <v>0.71</v>
+        <v>0.5</v>
       </c>
       <c r="P15" t="n">
-        <v>231.21</v>
+        <v>20.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>240.58</v>
+        <v>21.09</v>
       </c>
       <c r="R15" t="n">
-        <v>228.88</v>
+        <v>20.36</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
@@ -1416,60 +1416,60 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.26</v>
+        <v>16.2</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.41</v>
+        <v>-3.51</v>
       </c>
       <c r="E16" t="n">
-        <v>45.92</v>
+        <v>17.39</v>
       </c>
       <c r="F16" t="n">
-        <v>49.8</v>
+        <v>18.93</v>
       </c>
       <c r="G16" t="n">
-        <v>43.85</v>
+        <v>16.73</v>
       </c>
       <c r="H16" t="n">
-        <v>2.804</v>
+        <v>0.763</v>
       </c>
       <c r="I16" t="n">
-        <v>3.357</v>
+        <v>0.945</v>
       </c>
       <c r="J16" t="n">
-        <v>24.59</v>
+        <v>21.1</v>
       </c>
       <c r="K16" t="n">
-        <v>41.96</v>
+        <v>41.6</v>
       </c>
       <c r="L16" t="n">
-        <v>-10.14</v>
+        <v>-19.91</v>
       </c>
       <c r="M16" t="n">
-        <v>1921.34</v>
+        <v>1521.37</v>
       </c>
       <c r="N16" t="n">
-        <v>3175.6</v>
+        <v>1143.57</v>
       </c>
       <c r="O16" t="n">
-        <v>0.61</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
-        <v>44.05</v>
+        <v>16.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>45.32</v>
+        <v>16.52</v>
       </c>
       <c r="R16" t="n">
-        <v>43.65</v>
+        <v>16.03</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
@@ -1480,60 +1480,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.85</v>
+        <v>38.3</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.33</v>
+        <v>2.54</v>
       </c>
       <c r="E17" t="n">
-        <v>21.64</v>
+        <v>37.52</v>
       </c>
       <c r="F17" t="n">
-        <v>22.73</v>
+        <v>37.35</v>
       </c>
       <c r="G17" t="n">
-        <v>21</v>
+        <v>37.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0.531</v>
+        <v>-0.181</v>
       </c>
       <c r="I17" t="n">
-        <v>0.622</v>
+        <v>-0.27</v>
       </c>
       <c r="J17" t="n">
-        <v>21.22</v>
+        <v>51.67</v>
       </c>
       <c r="K17" t="n">
-        <v>37.06</v>
+        <v>47.63</v>
       </c>
       <c r="L17" t="n">
-        <v>-10.44</v>
+        <v>59.77</v>
       </c>
       <c r="M17" t="n">
-        <v>2033.72</v>
+        <v>6166.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4048.8</v>
+        <v>6004.59</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5</v>
+        <v>1.03</v>
       </c>
       <c r="P17" t="n">
-        <v>20.67</v>
+        <v>36.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>21.09</v>
+        <v>38.84</v>
       </c>
       <c r="R17" t="n">
-        <v>20.36</v>
+        <v>35.74</v>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
@@ -1544,60 +1544,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.2</v>
+        <v>17.5</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.51</v>
+        <v>0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>17.39</v>
+        <v>17.5</v>
       </c>
       <c r="F18" t="n">
-        <v>18.93</v>
+        <v>17.57</v>
       </c>
       <c r="G18" t="n">
-        <v>16.73</v>
+        <v>18.08</v>
       </c>
       <c r="H18" t="n">
-        <v>0.763</v>
+        <v>-0.324</v>
       </c>
       <c r="I18" t="n">
-        <v>0.945</v>
+        <v>-0.21</v>
       </c>
       <c r="J18" t="n">
-        <v>21.1</v>
+        <v>37.57</v>
       </c>
       <c r="K18" t="n">
-        <v>41.6</v>
+        <v>33.07</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.91</v>
+        <v>46.56</v>
       </c>
       <c r="M18" t="n">
-        <v>1521.37</v>
+        <v>14935.95</v>
       </c>
       <c r="N18" t="n">
-        <v>1143.57</v>
+        <v>28427.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>0.53</v>
       </c>
       <c r="P18" t="n">
-        <v>16.28</v>
+        <v>17.06</v>
       </c>
       <c r="Q18" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="R18" t="n">
         <v>16.52</v>
-      </c>
-      <c r="R18" t="n">
-        <v>16.03</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
@@ -1608,60 +1608,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38.3</v>
+        <v>49.9</v>
       </c>
       <c r="D19" t="n">
-        <v>2.54</v>
+        <v>-2.52</v>
       </c>
       <c r="E19" t="n">
-        <v>37.52</v>
+        <v>50.2</v>
       </c>
       <c r="F19" t="n">
-        <v>37.35</v>
+        <v>50.82</v>
       </c>
       <c r="G19" t="n">
-        <v>37.2</v>
+        <v>51.89</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.181</v>
+        <v>-1.592</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.27</v>
+        <v>-1.544</v>
       </c>
       <c r="J19" t="n">
-        <v>51.67</v>
+        <v>35.2</v>
       </c>
       <c r="K19" t="n">
-        <v>47.63</v>
+        <v>33.92</v>
       </c>
       <c r="L19" t="n">
-        <v>59.77</v>
+        <v>37.76</v>
       </c>
       <c r="M19" t="n">
-        <v>6166.9</v>
+        <v>6077.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6004.59</v>
+        <v>6709.75</v>
       </c>
       <c r="O19" t="n">
-        <v>1.03</v>
+        <v>0.91</v>
       </c>
       <c r="P19" t="n">
-        <v>36.35</v>
+        <v>49</v>
       </c>
       <c r="Q19" t="n">
-        <v>38.84</v>
+        <v>50.13</v>
       </c>
       <c r="R19" t="n">
-        <v>35.74</v>
+        <v>47.5</v>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
@@ -1672,60 +1672,60 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.5</v>
+        <v>46.4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4</v>
+        <v>-0.73</v>
       </c>
       <c r="E20" t="n">
-        <v>17.5</v>
+        <v>46.82</v>
       </c>
       <c r="F20" t="n">
-        <v>17.57</v>
+        <v>48.27</v>
       </c>
       <c r="G20" t="n">
-        <v>18.08</v>
+        <v>50.41</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.324</v>
+        <v>-2.555</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.21</v>
+        <v>-2.275</v>
       </c>
       <c r="J20" t="n">
-        <v>37.57</v>
+        <v>15.48</v>
       </c>
       <c r="K20" t="n">
-        <v>33.07</v>
+        <v>15.02</v>
       </c>
       <c r="L20" t="n">
-        <v>46.56</v>
+        <v>16.42</v>
       </c>
       <c r="M20" t="n">
-        <v>14935.95</v>
+        <v>2569.53</v>
       </c>
       <c r="N20" t="n">
-        <v>28427.2</v>
+        <v>3630.52</v>
       </c>
       <c r="O20" t="n">
-        <v>0.53</v>
+        <v>0.71</v>
       </c>
       <c r="P20" t="n">
-        <v>17.06</v>
+        <v>45.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.64</v>
+        <v>46.42</v>
       </c>
       <c r="R20" t="n">
-        <v>16.52</v>
+        <v>45.36</v>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
@@ -1736,60 +1736,60 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>49.9</v>
+        <v>14.4</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.52</v>
+        <v>0.98</v>
       </c>
       <c r="E21" t="n">
-        <v>50.2</v>
+        <v>14.21</v>
       </c>
       <c r="F21" t="n">
-        <v>50.82</v>
+        <v>14.48</v>
       </c>
       <c r="G21" t="n">
-        <v>51.89</v>
+        <v>15.33</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.592</v>
+        <v>-1.345</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.544</v>
+        <v>-1.453</v>
       </c>
       <c r="J21" t="n">
-        <v>35.2</v>
+        <v>30.2</v>
       </c>
       <c r="K21" t="n">
-        <v>33.92</v>
+        <v>22.17</v>
       </c>
       <c r="L21" t="n">
-        <v>37.76</v>
+        <v>46.25</v>
       </c>
       <c r="M21" t="n">
-        <v>6077.55</v>
+        <v>15286.23</v>
       </c>
       <c r="N21" t="n">
-        <v>6709.75</v>
+        <v>25481.22</v>
       </c>
       <c r="O21" t="n">
-        <v>0.91</v>
+        <v>0.6</v>
       </c>
       <c r="P21" t="n">
-        <v>49</v>
+        <v>14.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>50.13</v>
+        <v>14.4</v>
       </c>
       <c r="R21" t="n">
-        <v>47.5</v>
+        <v>13.92</v>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
@@ -1800,60 +1800,60 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>46.4</v>
+        <v>58.85</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.73</v>
+        <v>-0.88</v>
       </c>
       <c r="E22" t="n">
-        <v>46.82</v>
+        <v>59.83</v>
       </c>
       <c r="F22" t="n">
-        <v>48.27</v>
+        <v>61.96</v>
       </c>
       <c r="G22" t="n">
-        <v>50.41</v>
+        <v>64.88</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.555</v>
+        <v>-3.295</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.275</v>
+        <v>-2.734</v>
       </c>
       <c r="J22" t="n">
-        <v>15.48</v>
+        <v>12.78</v>
       </c>
       <c r="K22" t="n">
-        <v>15.02</v>
+        <v>12.04</v>
       </c>
       <c r="L22" t="n">
-        <v>16.42</v>
+        <v>14.28</v>
       </c>
       <c r="M22" t="n">
-        <v>2569.53</v>
+        <v>980.66</v>
       </c>
       <c r="N22" t="n">
-        <v>3630.52</v>
+        <v>1327.95</v>
       </c>
       <c r="O22" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="P22" t="n">
-        <v>45.98</v>
+        <v>58.31</v>
       </c>
       <c r="Q22" t="n">
-        <v>46.42</v>
+        <v>58.88</v>
       </c>
       <c r="R22" t="n">
-        <v>45.36</v>
+        <v>57.02</v>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
@@ -1864,60 +1864,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14.4</v>
+        <v>28.68</v>
       </c>
       <c r="D23" t="n">
-        <v>0.98</v>
+        <v>4.82</v>
       </c>
       <c r="E23" t="n">
-        <v>14.21</v>
+        <v>27.64</v>
       </c>
       <c r="F23" t="n">
-        <v>14.48</v>
+        <v>28.47</v>
       </c>
       <c r="G23" t="n">
-        <v>15.33</v>
+        <v>30.04</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.345</v>
+        <v>-0.588</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.453</v>
+        <v>-0.187</v>
       </c>
       <c r="J23" t="n">
-        <v>30.2</v>
+        <v>38.79</v>
       </c>
       <c r="K23" t="n">
-        <v>22.17</v>
+        <v>32.32</v>
       </c>
       <c r="L23" t="n">
-        <v>46.25</v>
+        <v>51.73</v>
       </c>
       <c r="M23" t="n">
-        <v>15286.23</v>
+        <v>23578.97</v>
       </c>
       <c r="N23" t="n">
-        <v>25481.22</v>
+        <v>23861.58</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6</v>
+        <v>0.99</v>
       </c>
       <c r="P23" t="n">
-        <v>14.04</v>
+        <v>27.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>14.4</v>
+        <v>29.3</v>
       </c>
       <c r="R23" t="n">
-        <v>13.92</v>
+        <v>27.1</v>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
@@ -1928,60 +1928,60 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>58.85</v>
+        <v>27.72</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.88</v>
+        <v>0.98</v>
       </c>
       <c r="E24" t="n">
-        <v>59.83</v>
+        <v>27.84</v>
       </c>
       <c r="F24" t="n">
-        <v>61.96</v>
+        <v>28.52</v>
       </c>
       <c r="G24" t="n">
-        <v>64.88</v>
+        <v>28.79</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.295</v>
+        <v>0.124</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.734</v>
+        <v>0.446</v>
       </c>
       <c r="J24" t="n">
-        <v>12.78</v>
+        <v>16.28</v>
       </c>
       <c r="K24" t="n">
-        <v>12.04</v>
+        <v>21.79</v>
       </c>
       <c r="L24" t="n">
-        <v>14.28</v>
+        <v>5.26</v>
       </c>
       <c r="M24" t="n">
-        <v>980.66</v>
+        <v>19398.99</v>
       </c>
       <c r="N24" t="n">
-        <v>1327.95</v>
+        <v>28230.52</v>
       </c>
       <c r="O24" t="n">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>58.31</v>
+        <v>27.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>58.88</v>
+        <v>28.36</v>
       </c>
       <c r="R24" t="n">
-        <v>57.02</v>
+        <v>27.46</v>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
@@ -1992,60 +1992,60 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28.68</v>
+        <v>135.53</v>
       </c>
       <c r="D25" t="n">
-        <v>4.82</v>
+        <v>-1.36</v>
       </c>
       <c r="E25" t="n">
-        <v>27.64</v>
+        <v>137.55</v>
       </c>
       <c r="F25" t="n">
-        <v>28.47</v>
+        <v>131.99</v>
       </c>
       <c r="G25" t="n">
-        <v>30.04</v>
+        <v>119.27</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.588</v>
+        <v>8.522</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.187</v>
+        <v>6.518</v>
       </c>
       <c r="J25" t="n">
-        <v>38.79</v>
+        <v>79.73</v>
       </c>
       <c r="K25" t="n">
-        <v>32.32</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>51.73</v>
+        <v>79.27</v>
       </c>
       <c r="M25" t="n">
-        <v>23578.97</v>
+        <v>693.97</v>
       </c>
       <c r="N25" t="n">
-        <v>23861.58</v>
+        <v>764.95</v>
       </c>
       <c r="O25" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="P25" t="n">
-        <v>27.1</v>
+        <v>133.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>29.3</v>
+        <v>141.41</v>
       </c>
       <c r="R25" t="n">
-        <v>27.1</v>
+        <v>131.83</v>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
@@ -2056,60 +2056,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>27.72</v>
+        <v>32.78</v>
       </c>
       <c r="D26" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="E26" t="n">
-        <v>27.84</v>
+        <v>32.56</v>
       </c>
       <c r="F26" t="n">
-        <v>28.52</v>
+        <v>32.71</v>
       </c>
       <c r="G26" t="n">
-        <v>28.79</v>
+        <v>34.84</v>
       </c>
       <c r="H26" t="n">
-        <v>0.124</v>
+        <v>-1.908</v>
       </c>
       <c r="I26" t="n">
-        <v>0.446</v>
+        <v>-1.864</v>
       </c>
       <c r="J26" t="n">
-        <v>16.28</v>
+        <v>43.94</v>
       </c>
       <c r="K26" t="n">
-        <v>21.79</v>
+        <v>34.43</v>
       </c>
       <c r="L26" t="n">
-        <v>5.26</v>
+        <v>62.96</v>
       </c>
       <c r="M26" t="n">
-        <v>19398.99</v>
+        <v>23690.1</v>
       </c>
       <c r="N26" t="n">
-        <v>28230.52</v>
+        <v>31535.3</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="P26" t="n">
-        <v>27.46</v>
+        <v>32.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>28.36</v>
+        <v>32.8</v>
       </c>
       <c r="R26" t="n">
-        <v>27.46</v>
+        <v>31.88</v>
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
@@ -2120,60 +2120,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>135.53</v>
+        <v>6.49</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.36</v>
+        <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>137.55</v>
+        <v>6.07</v>
       </c>
       <c r="F27" t="n">
-        <v>131.99</v>
+        <v>6.16</v>
       </c>
       <c r="G27" t="n">
-        <v>119.27</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>8.522</v>
+        <v>-0.356</v>
       </c>
       <c r="I27" t="n">
-        <v>6.518</v>
+        <v>-0.308</v>
       </c>
       <c r="J27" t="n">
-        <v>79.73</v>
+        <v>34.34</v>
       </c>
       <c r="K27" t="n">
-        <v>79.95999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="L27" t="n">
-        <v>79.27</v>
+        <v>62.84</v>
       </c>
       <c r="M27" t="n">
-        <v>693.97</v>
+        <v>56862.5</v>
       </c>
       <c r="N27" t="n">
-        <v>764.95</v>
+        <v>31175.02</v>
       </c>
       <c r="O27" t="n">
-        <v>0.91</v>
+        <v>1.82</v>
       </c>
       <c r="P27" t="n">
-        <v>133.58</v>
+        <v>6.27</v>
       </c>
       <c r="Q27" t="n">
-        <v>141.41</v>
+        <v>6.49</v>
       </c>
       <c r="R27" t="n">
-        <v>131.83</v>
+        <v>6.1</v>
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
@@ -2184,60 +2184,60 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32.78</v>
+        <v>9.51</v>
       </c>
       <c r="D28" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="E28" t="n">
-        <v>32.56</v>
+        <v>9.42</v>
       </c>
       <c r="F28" t="n">
-        <v>32.71</v>
+        <v>9.35</v>
       </c>
       <c r="G28" t="n">
-        <v>34.84</v>
+        <v>9.18</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.908</v>
+        <v>0.159</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.864</v>
+        <v>0.134</v>
       </c>
       <c r="J28" t="n">
-        <v>43.94</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>34.43</v>
+        <v>84.28</v>
       </c>
       <c r="L28" t="n">
-        <v>62.96</v>
+        <v>86.31</v>
       </c>
       <c r="M28" t="n">
-        <v>23690.1</v>
+        <v>11863.78</v>
       </c>
       <c r="N28" t="n">
-        <v>31535.3</v>
+        <v>10818.86</v>
       </c>
       <c r="O28" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="P28" t="n">
-        <v>32.2</v>
+        <v>9.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>32.8</v>
+        <v>9.57</v>
       </c>
       <c r="R28" t="n">
-        <v>31.88</v>
+        <v>9.31</v>
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
@@ -2248,60 +2248,60 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.49</v>
+        <v>5.84</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>-0.85</v>
       </c>
       <c r="E29" t="n">
-        <v>6.07</v>
+        <v>5.92</v>
       </c>
       <c r="F29" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
       <c r="G29" t="n">
-        <v>6.8</v>
+        <v>6.28</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.356</v>
+        <v>-0.242</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.308</v>
+        <v>-0.207</v>
       </c>
       <c r="J29" t="n">
-        <v>34.34</v>
+        <v>9.18</v>
       </c>
       <c r="K29" t="n">
-        <v>20.08</v>
+        <v>10.87</v>
       </c>
       <c r="L29" t="n">
-        <v>62.84</v>
+        <v>5.82</v>
       </c>
       <c r="M29" t="n">
-        <v>56862.5</v>
+        <v>7514.07</v>
       </c>
       <c r="N29" t="n">
-        <v>31175.02</v>
+        <v>12276.88</v>
       </c>
       <c r="O29" t="n">
-        <v>1.82</v>
+        <v>0.61</v>
       </c>
       <c r="P29" t="n">
-        <v>6.27</v>
+        <v>5.82</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.49</v>
+        <v>5.86</v>
       </c>
       <c r="R29" t="n">
-        <v>6.1</v>
+        <v>5.77</v>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
@@ -2312,60 +2312,60 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.51</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.96</v>
+        <v>-0.02</v>
       </c>
       <c r="E30" t="n">
-        <v>9.42</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>9.35</v>
+        <v>95.2</v>
       </c>
       <c r="G30" t="n">
-        <v>9.18</v>
+        <v>95.63</v>
       </c>
       <c r="H30" t="n">
-        <v>0.159</v>
+        <v>-0.461</v>
       </c>
       <c r="I30" t="n">
-        <v>0.134</v>
+        <v>-0.067</v>
       </c>
       <c r="J30" t="n">
-        <v>84.95999999999999</v>
+        <v>17.03</v>
       </c>
       <c r="K30" t="n">
-        <v>84.28</v>
+        <v>26.56</v>
       </c>
       <c r="L30" t="n">
-        <v>86.31</v>
+        <v>-2.04</v>
       </c>
       <c r="M30" t="n">
-        <v>11863.78</v>
+        <v>948.13</v>
       </c>
       <c r="N30" t="n">
-        <v>10818.86</v>
+        <v>1113.81</v>
       </c>
       <c r="O30" t="n">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="P30" t="n">
-        <v>9.33</v>
+        <v>93</v>
       </c>
       <c r="Q30" t="n">
-        <v>9.57</v>
+        <v>93.53</v>
       </c>
       <c r="R30" t="n">
-        <v>9.31</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
@@ -2376,60 +2376,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.84</v>
+        <v>36.76</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="E31" t="n">
-        <v>5.92</v>
+        <v>36.53</v>
       </c>
       <c r="F31" t="n">
-        <v>6.08</v>
+        <v>36.59</v>
       </c>
       <c r="G31" t="n">
-        <v>6.28</v>
+        <v>36.89</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.242</v>
+        <v>-0.315</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.207</v>
+        <v>-0.33</v>
       </c>
       <c r="J31" t="n">
-        <v>9.18</v>
+        <v>53.74</v>
       </c>
       <c r="K31" t="n">
-        <v>10.87</v>
+        <v>44.17</v>
       </c>
       <c r="L31" t="n">
-        <v>5.82</v>
+        <v>72.87</v>
       </c>
       <c r="M31" t="n">
-        <v>7514.07</v>
+        <v>1263.27</v>
       </c>
       <c r="N31" t="n">
-        <v>12276.88</v>
+        <v>2235.34</v>
       </c>
       <c r="O31" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="P31" t="n">
-        <v>5.82</v>
+        <v>36.72</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.86</v>
+        <v>37.07</v>
       </c>
       <c r="R31" t="n">
-        <v>5.77</v>
+        <v>36.65</v>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
@@ -2440,60 +2440,60 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.40000000000001</v>
+        <v>13.53</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.02</v>
+        <v>-1.46</v>
       </c>
       <c r="E32" t="n">
-        <v>93.68000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="F32" t="n">
-        <v>95.2</v>
+        <v>13.96</v>
       </c>
       <c r="G32" t="n">
-        <v>95.63</v>
+        <v>12.6</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.461</v>
+        <v>1.053</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.067</v>
+        <v>0.999</v>
       </c>
       <c r="J32" t="n">
-        <v>17.03</v>
+        <v>56.04</v>
       </c>
       <c r="K32" t="n">
-        <v>26.56</v>
+        <v>67.98</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.04</v>
+        <v>32.18</v>
       </c>
       <c r="M32" t="n">
-        <v>948.13</v>
+        <v>5791.29</v>
       </c>
       <c r="N32" t="n">
-        <v>1113.81</v>
+        <v>7252.99</v>
       </c>
       <c r="O32" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="P32" t="n">
-        <v>93</v>
+        <v>13.47</v>
       </c>
       <c r="Q32" t="n">
-        <v>93.53</v>
+        <v>13.84</v>
       </c>
       <c r="R32" t="n">
-        <v>92.29000000000001</v>
+        <v>13.03</v>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
@@ -2504,60 +2504,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>36.76</v>
+        <v>17.93</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.84</v>
+        <v>-1.59</v>
       </c>
       <c r="E33" t="n">
-        <v>36.53</v>
+        <v>17.96</v>
       </c>
       <c r="F33" t="n">
-        <v>36.59</v>
+        <v>18.13</v>
       </c>
       <c r="G33" t="n">
-        <v>36.89</v>
+        <v>19.17</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.315</v>
+        <v>-0.597</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.33</v>
+        <v>-0.432</v>
       </c>
       <c r="J33" t="n">
-        <v>53.74</v>
+        <v>38.29</v>
       </c>
       <c r="K33" t="n">
-        <v>44.17</v>
+        <v>28.51</v>
       </c>
       <c r="L33" t="n">
-        <v>72.87</v>
+        <v>57.84</v>
       </c>
       <c r="M33" t="n">
-        <v>1263.27</v>
+        <v>4083.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2235.34</v>
+        <v>5107.03</v>
       </c>
       <c r="O33" t="n">
-        <v>0.57</v>
+        <v>0.8</v>
       </c>
       <c r="P33" t="n">
-        <v>36.72</v>
+        <v>17.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>37.07</v>
+        <v>18.77</v>
       </c>
       <c r="R33" t="n">
-        <v>36.65</v>
+        <v>17.7</v>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
@@ -2568,60 +2568,60 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13.53</v>
+        <v>31.43</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.46</v>
+        <v>-2.24</v>
       </c>
       <c r="E34" t="n">
-        <v>14.55</v>
+        <v>31.88</v>
       </c>
       <c r="F34" t="n">
-        <v>13.96</v>
+        <v>32.5</v>
       </c>
       <c r="G34" t="n">
-        <v>12.6</v>
+        <v>34.05</v>
       </c>
       <c r="H34" t="n">
-        <v>1.053</v>
+        <v>-2.091</v>
       </c>
       <c r="I34" t="n">
-        <v>0.999</v>
+        <v>-2.073</v>
       </c>
       <c r="J34" t="n">
-        <v>56.04</v>
+        <v>18.54</v>
       </c>
       <c r="K34" t="n">
-        <v>67.98</v>
+        <v>19.38</v>
       </c>
       <c r="L34" t="n">
-        <v>32.18</v>
+        <v>16.87</v>
       </c>
       <c r="M34" t="n">
-        <v>5791.29</v>
+        <v>2764.53</v>
       </c>
       <c r="N34" t="n">
-        <v>7252.99</v>
+        <v>4055.24</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8</v>
+        <v>0.68</v>
       </c>
       <c r="P34" t="n">
-        <v>13.47</v>
+        <v>31.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>13.84</v>
+        <v>31.84</v>
       </c>
       <c r="R34" t="n">
-        <v>13.03</v>
+        <v>30.9</v>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
@@ -2632,60 +2632,60 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17.93</v>
+        <v>47.82</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.59</v>
+        <v>0.67</v>
       </c>
       <c r="E35" t="n">
-        <v>17.96</v>
+        <v>47.75</v>
       </c>
       <c r="F35" t="n">
-        <v>18.13</v>
+        <v>48.25</v>
       </c>
       <c r="G35" t="n">
-        <v>19.17</v>
+        <v>47.74</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.597</v>
+        <v>1.153</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.432</v>
+        <v>1.435</v>
       </c>
       <c r="J35" t="n">
-        <v>38.29</v>
+        <v>35.84</v>
       </c>
       <c r="K35" t="n">
-        <v>28.51</v>
+        <v>46.95</v>
       </c>
       <c r="L35" t="n">
-        <v>57.84</v>
+        <v>13.63</v>
       </c>
       <c r="M35" t="n">
-        <v>4083.75</v>
+        <v>2812.65</v>
       </c>
       <c r="N35" t="n">
-        <v>5107.03</v>
+        <v>4898.09</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="P35" t="n">
-        <v>17.77</v>
+        <v>47.89</v>
       </c>
       <c r="Q35" t="n">
-        <v>18.77</v>
+        <v>48.43</v>
       </c>
       <c r="R35" t="n">
-        <v>17.7</v>
+        <v>47.62</v>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
@@ -2696,60 +2696,60 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>31.43</v>
+        <v>4.9</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.24</v>
+        <v>1.03</v>
       </c>
       <c r="E36" t="n">
-        <v>31.88</v>
+        <v>4.77</v>
       </c>
       <c r="F36" t="n">
-        <v>32.5</v>
+        <v>4.89</v>
       </c>
       <c r="G36" t="n">
-        <v>34.05</v>
+        <v>5.4</v>
       </c>
       <c r="H36" t="n">
-        <v>-2.091</v>
+        <v>-0.286</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.073</v>
+        <v>-0.213</v>
       </c>
       <c r="J36" t="n">
-        <v>18.54</v>
+        <v>26.96</v>
       </c>
       <c r="K36" t="n">
-        <v>19.38</v>
+        <v>18.96</v>
       </c>
       <c r="L36" t="n">
-        <v>16.87</v>
+        <v>42.97</v>
       </c>
       <c r="M36" t="n">
-        <v>2764.53</v>
+        <v>3637.94</v>
       </c>
       <c r="N36" t="n">
-        <v>4055.24</v>
+        <v>5112.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="P36" t="n">
-        <v>31.58</v>
+        <v>4.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>31.84</v>
+        <v>4.92</v>
       </c>
       <c r="R36" t="n">
-        <v>30.9</v>
+        <v>4.74</v>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
@@ -2760,191 +2760,63 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47.82</v>
+        <v>33.22</v>
       </c>
       <c r="D37" t="n">
-        <v>0.67</v>
+        <v>-2.09</v>
       </c>
       <c r="E37" t="n">
-        <v>47.75</v>
+        <v>34.36</v>
       </c>
       <c r="F37" t="n">
-        <v>48.25</v>
+        <v>34.62</v>
       </c>
       <c r="G37" t="n">
-        <v>47.74</v>
+        <v>35.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.153</v>
+        <v>0.334</v>
       </c>
       <c r="I37" t="n">
-        <v>1.435</v>
+        <v>0.895</v>
       </c>
       <c r="J37" t="n">
-        <v>35.84</v>
+        <v>23.76</v>
       </c>
       <c r="K37" t="n">
-        <v>46.95</v>
+        <v>24.77</v>
       </c>
       <c r="L37" t="n">
-        <v>13.63</v>
+        <v>21.74</v>
       </c>
       <c r="M37" t="n">
-        <v>2812.65</v>
+        <v>3407.57</v>
       </c>
       <c r="N37" t="n">
-        <v>4898.09</v>
+        <v>5863.85</v>
       </c>
       <c r="O37" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="P37" t="n">
-        <v>47.89</v>
+        <v>33.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>48.43</v>
+        <v>33.77</v>
       </c>
       <c r="R37" t="n">
-        <v>47.62</v>
+        <v>32.43</v>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>600963</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>岳阳林纸</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E38" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="F38" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="G38" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-0.286</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-0.213</v>
-      </c>
-      <c r="J38" t="n">
-        <v>26.96</v>
-      </c>
-      <c r="K38" t="n">
-        <v>18.96</v>
-      </c>
-      <c r="L38" t="n">
-        <v>42.97</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3637.94</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5112.7</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="R38" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>601877</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>正泰电器</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>33.22</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="E39" t="n">
-        <v>34.36</v>
-      </c>
-      <c r="F39" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="G39" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="J39" t="n">
-        <v>23.76</v>
-      </c>
-      <c r="K39" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="L39" t="n">
-        <v>21.74</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3407.57</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5863.85</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="P39" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>33.77</v>
-      </c>
-      <c r="R39" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
